--- a/output/2026-09-12_22_Croazia_Karlovacka_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-12_22_Croazia_Karlovacka_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -540,10 +540,9 @@
           <t>+385 47 844 741</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distribuzione utensili e macchine per lavorazione meccanica dei metalli: utensili da taglio, macchine per filettatura, trafilatura, macchinari per tubi. Core business coerente al 100% col metalworking.</t>
+          <t>Distribuzione utensili e macchine per lavorazione meccanica dei metalli: utensili da taglio, macchine per filettatura, trafilatura, macchinari per tubi. Core business coerente al 100% col metalworking. [DUPLICATO — vedi anche: 2026-09-12_20_Croazia_Karlovacka_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +584,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Commercio all'ingrosso di macchine utensili, utensili da taglio; servizi di ripristino/rivestimento utensili, retrofit macchine, scansione/misura 3D. Fondata 1998.</t>
+          <t>Commercio all'ingrosso di macchine utensili, utensili da taglio; servizi di ripristino/rivestimento utensili, retrofit macchine, scansione/misura 3D. Fondata 1998. [DUPLICATO — vedi anche: 2026-09-12_20_Croazia_Karlovacka_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/output/2026-09-12_22_Croazia_Karlovacka_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-12_22_Croazia_Karlovacka_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
